--- a/AAII_Financials/Quarterly/ATVK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ATVK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="92">
   <si>
     <t>ATVK</t>
   </si>
@@ -1990,10 +1990,10 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F49" s="3">
         <v>2000</v>
@@ -2094,11 +2094,11 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>100</v>
-      </c>
-      <c r="E52" s="3">
-        <v>100</v>
+      <c r="D52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F52" s="3">
         <v>100</v>
